--- a/Collections/Canada/#Canada#Commemorative#[2003-present]#circulation_quality.xlsx
+++ b/Collections/Canada/#Canada#Commemorative#[2003-present]#circulation_quality.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\Canada\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{841FB247-3685-4BB7-B20A-C88D743F6995}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F9F25E05-4620-43A7-9858-8C637D767D47}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -270,7 +270,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="713" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="722" uniqueCount="151">
   <si>
     <t>-</t>
   </si>
@@ -729,11 +729,19 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <charset val="204"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1022,23 +1030,23 @@
   </borders>
   <cellStyleXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="10" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="48">
+  <cellXfs count="50">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="2" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="2" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1050,84 +1058,93 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" xfId="4" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="1" xfId="5" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="1" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="5" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="7" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="5" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="5" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
@@ -1135,34 +1152,31 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="5" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="3" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="4" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="5" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="9" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="0" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="3" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="7" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="6" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1184,78 +1198,6 @@
   </cellStyles>
   <dxfs count="538">
     <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor rgb="FF9BE5FF"/>
-          <bgColor rgb="FF9BE5FF"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
@@ -1263,6 +1205,78 @@
     </dxf>
     <dxf>
       <alignment vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
     </dxf>
     <dxf>
       <fill>
@@ -5501,9 +5515,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="11"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="10" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="9"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -5806,7 +5820,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AE0B4963-DC2E-4382-9FF8-510C6ADD856E}">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:I43"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" customWidth="1"/>
@@ -5818,25 +5832,25 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="39" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="40"/>
-      <c r="E1" s="41" t="s">
+      <c r="D1" s="42"/>
+      <c r="E1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="F1" s="42"/>
-      <c r="G1" s="43" t="s">
+      <c r="F1" s="44"/>
+      <c r="G1" s="45" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="44"/>
+      <c r="H1" s="46"/>
     </row>
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
+      <c r="A2" s="40"/>
       <c r="B2" s="27" t="s">
         <v>8</v>
       </c>
@@ -7018,6 +7032,36 @@
       </c>
       <c r="I42" s="21" t="str">
         <f t="shared" si="0"/>
+        <v/>
+      </c>
+    </row>
+    <row r="43" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A43" s="11">
+        <v>2025</v>
+      </c>
+      <c r="B43" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="C43" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="D43" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="E43" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="F43" s="9" t="s">
+        <v>0</v>
+      </c>
+      <c r="G43" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="H43" s="4" t="s">
+        <v>0</v>
+      </c>
+      <c r="I43" s="21" t="str">
+        <f t="shared" ref="I43" si="1">IF(OR(AND(G43&gt;1,G43&lt;&gt;"-"),AND(H43&gt;1,H43&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -7345,7 +7389,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G36:H42">
+  <conditionalFormatting sqref="G36:H43">
     <cfRule type="colorScale" priority="11">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -7357,52 +7401,52 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G36:H42">
+  <conditionalFormatting sqref="G36:H43">
     <cfRule type="containsText" dxfId="481" priority="10" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G36:H42">
+  <conditionalFormatting sqref="G36:H43">
     <cfRule type="containsText" dxfId="480" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G36:G42">
+  <conditionalFormatting sqref="G36:G43">
     <cfRule type="containsText" dxfId="479" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G36:G42">
+  <conditionalFormatting sqref="G36:G43">
     <cfRule type="containsText" dxfId="478" priority="8" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H36:H42">
+  <conditionalFormatting sqref="H36:H43">
     <cfRule type="containsText" dxfId="477" priority="6" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H36:H42">
+  <conditionalFormatting sqref="H36:H43">
     <cfRule type="containsText" dxfId="476" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H36:H42">
+  <conditionalFormatting sqref="H36:H43">
     <cfRule type="containsText" dxfId="475" priority="4" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G36:G42">
+  <conditionalFormatting sqref="G36:G43">
     <cfRule type="containsText" dxfId="474" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G36:G42">
+  <conditionalFormatting sqref="G36:G43">
     <cfRule type="containsText" dxfId="473" priority="2" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="G36:G42">
+  <conditionalFormatting sqref="G36:G43">
     <cfRule type="containsText" dxfId="472" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
@@ -7427,26 +7471,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="39" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="24"/>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="45"/>
+      <c r="D1" s="47"/>
       <c r="E1" s="30"/>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="42"/>
-      <c r="H1" s="43" t="s">
+      <c r="G1" s="44"/>
+      <c r="H1" s="45" t="s">
         <v>60</v>
       </c>
-      <c r="I1" s="44"/>
+      <c r="I1" s="46"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
+      <c r="A2" s="40"/>
       <c r="B2" s="25" t="s">
         <v>8</v>
       </c>
@@ -8333,7 +8377,9 @@
         <v>97</v>
       </c>
       <c r="E32" s="23"/>
-      <c r="F32" s="19"/>
+      <c r="F32" s="19" t="s">
+        <v>93</v>
+      </c>
       <c r="G32" s="9" t="s">
         <v>0</v>
       </c>
@@ -8352,7 +8398,7 @@
       <c r="A33" s="11">
         <v>2024</v>
       </c>
-      <c r="B33" s="22" t="s">
+      <c r="B33" s="48" t="s">
         <v>96</v>
       </c>
       <c r="C33" s="23"/>
@@ -8362,7 +8408,9 @@
       <c r="E33" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="F33" s="19"/>
+      <c r="F33" s="49" t="s">
+        <v>105</v>
+      </c>
       <c r="G33" s="9" t="s">
         <v>0</v>
       </c>
@@ -8381,7 +8429,7 @@
       <c r="A34" s="11">
         <v>2025</v>
       </c>
-      <c r="B34" s="26" t="s">
+      <c r="B34" s="48" t="s">
         <v>99</v>
       </c>
       <c r="C34" s="13"/>
@@ -8441,7 +8489,7 @@
     <mergeCell ref="F1:G1"/>
     <mergeCell ref="H1:I1"/>
   </mergeCells>
-  <phoneticPr fontId="16" type="noConversion"/>
+  <phoneticPr fontId="17" type="noConversion"/>
   <conditionalFormatting sqref="H4:I4">
     <cfRule type="colorScale" priority="292">
       <colorScale>
@@ -8636,7 +8684,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9 I5 I11 I13 I15 I17 I19 I21 I23">
+  <conditionalFormatting sqref="I5 I9 I11 I13 I15 I17 I19 I21 I23">
     <cfRule type="colorScale" priority="200">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8673,7 +8721,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H9 H5 H11 H13 H15 H17 H19 H21 H23">
+  <conditionalFormatting sqref="H5 H9 H11 H13 H15 H17 H19 H21 H23">
     <cfRule type="colorScale" priority="192">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8705,7 +8753,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I8 I6 I10 I12 I14 I20">
+  <conditionalFormatting sqref="I6 I8 I10 I12 I14 I20">
     <cfRule type="colorScale" priority="187">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -8742,7 +8790,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H8 H6 H10 H12 H14 H20">
+  <conditionalFormatting sqref="H6 H8 H10 H12 H14 H20">
     <cfRule type="colorScale" priority="181">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -9716,26 +9764,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="37" t="s">
+      <c r="A1" s="39" t="s">
         <v>2</v>
       </c>
       <c r="B1" s="32"/>
-      <c r="C1" s="39" t="s">
+      <c r="C1" s="41" t="s">
         <v>4</v>
       </c>
-      <c r="D1" s="45"/>
+      <c r="D1" s="47"/>
       <c r="E1" s="30"/>
-      <c r="F1" s="41" t="s">
+      <c r="F1" s="43" t="s">
         <v>3</v>
       </c>
-      <c r="G1" s="42"/>
-      <c r="H1" s="43" t="s">
+      <c r="G1" s="44"/>
+      <c r="H1" s="45" t="s">
         <v>103</v>
       </c>
-      <c r="I1" s="44"/>
+      <c r="I1" s="46"/>
     </row>
     <row r="2" spans="1:10" ht="15" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="38"/>
+      <c r="A2" s="40"/>
       <c r="B2" s="33" t="s">
         <v>8</v>
       </c>
@@ -11124,7 +11172,7 @@
       <c r="A48" s="11">
         <v>2025</v>
       </c>
-      <c r="B48" s="46" t="s">
+      <c r="B48" s="37" t="s">
         <v>148</v>
       </c>
       <c r="C48" s="13"/>
@@ -11132,7 +11180,7 @@
         <v>97</v>
       </c>
       <c r="E48" s="23"/>
-      <c r="F48" s="47" t="s">
+      <c r="F48" s="38" t="s">
         <v>150</v>
       </c>
       <c r="G48" s="9" t="s">
@@ -11153,7 +11201,7 @@
       <c r="A49" s="11">
         <v>2025</v>
       </c>
-      <c r="B49" s="46" t="s">
+      <c r="B49" s="37" t="s">
         <v>148</v>
       </c>
       <c r="C49" s="13"/>
@@ -11163,7 +11211,7 @@
       <c r="E49" s="23" t="s">
         <v>98</v>
       </c>
-      <c r="F49" s="47" t="s">
+      <c r="F49" s="38" t="s">
         <v>149</v>
       </c>
       <c r="G49" s="9" t="s">
@@ -11330,7 +11378,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I16 I12 I19 I23 I28 I34 I38">
+  <conditionalFormatting sqref="I12 I16 I19 I23 I28 I34 I38">
     <cfRule type="colorScale" priority="483">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11367,7 +11415,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H16 H12 H19 H23 H28 H34 H38">
+  <conditionalFormatting sqref="H12 H16 H19 H23 H28 H34 H38">
     <cfRule type="colorScale" priority="477">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11399,7 +11447,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I9 I6 I11 I14 I17 I30">
+  <conditionalFormatting sqref="I6 I9 I11 I14 I17 I30">
     <cfRule type="colorScale" priority="472">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -11436,7 +11484,7 @@
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="H11 H6 H14 H17 H30">
+  <conditionalFormatting sqref="H6 H11 H14 H17 H30">
     <cfRule type="colorScale" priority="466">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -13339,42 +13387,42 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I48:I49">
-    <cfRule type="containsText" dxfId="8" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="11" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I48:I49">
-    <cfRule type="containsText" dxfId="7" priority="6" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="10" priority="6" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H48:H49">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="9" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I48:I49">
-    <cfRule type="containsText" dxfId="5" priority="10" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="8" priority="10" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I48:I49">
-    <cfRule type="containsText" dxfId="4" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="7" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="I48:I49">
-    <cfRule type="containsText" dxfId="3" priority="8" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="6" priority="8" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H48:H49">
-    <cfRule type="containsText" dxfId="2" priority="4" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="5" priority="4" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H48:H49">
-    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
@@ -13391,7 +13439,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="H48:H49">
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="3" priority="2" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(#REF!))))</formula>
     </cfRule>
   </conditionalFormatting>
